--- a/demo_data/hospital_master.xlsx
+++ b/demo_data/hospital_master.xlsx
@@ -454,18 +454,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>892</v>
+        <v>734</v>
       </c>
     </row>
     <row r="3">
@@ -475,18 +475,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>605</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>625</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>499</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6">
@@ -538,18 +538,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>361</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -559,18 +559,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>540</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -580,18 +580,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>479</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10">
@@ -626,14 +626,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>409</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11">
@@ -643,24 +643,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>905</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -668,41 +668,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nephrology</t>
+          <t>Orthopaedics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>874</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Gynaecology</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -710,35 +710,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>977</v>
+        <v>805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Orthopaedics</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>37</v>
       </c>
       <c r="E15" t="n">
-        <v>409</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -756,41 +756,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>304</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paediatrics</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>235</v>
+        <v>988</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -798,73 +798,73 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>280</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>680</v>
+        <v>809</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gynaecology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>937</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>110</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1006,14 +1006,14 @@
         </is>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>English, Hindi</t>
+          <t>English, Tamil</t>
         </is>
       </c>
     </row>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1072,14 +1072,14 @@
         </is>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>English, Kannada</t>
+          <t>English, Hindi</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
         </is>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>English, Kannada</t>
+          <t>English, Tamil</t>
         </is>
       </c>
     </row>
@@ -1141,11 +1141,11 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>English, Tamil</t>
+          <t>English, Hindi</t>
         </is>
       </c>
     </row>
@@ -1171,14 +1171,14 @@
         </is>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>English, Kannada</t>
+          <t>English, Hindi</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1204,14 @@
         </is>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>English, Hindi</t>
+          <t>English, Kannada</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
